--- a/Ministry_of_Justice.xlsx
+++ b/Ministry_of_Justice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E276"/>
+  <dimension ref="A1:E298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13556,6 +13556,1414 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/news-details/1457/2</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>ويلغي المرسوم الجديد صراحةً المرسومين رقم 14115/2024 ورقم 14555/2025، ويعتمد إطاراً تنفيذياً مرحلياً يتيح للإدارات العامة البدء بتطبيق أحكامه من دون انتظار اكتمال البنية الوطنية للاعتماد، وفق المعايير التقنية المعتمدة في التنظيم الأوروبي eIDAS، مع ضمان توطين العناصر الجوهرية لخدمات الثقة على الأراضي اللبنانية.
+ويهدف المرسوم إلى وضع أحكام القانون رقم 81/2018 موضع التطبيق الفعلي، من خلال توفير إطار واضح لإنشاء الأسناد الرسمية الإلكترونية وتوقيعها وتبادلها وحفظها، بما يتيح تقليص الاعتماد على المعاملات الورقية، والحد من التأخير والكلفة، وتخفيف حاجة المواطنين إلى الحضور الشخصي لإنجاز معاملاتهم.
+كما يحدّد المرسوم شروط التحقق من صحة السند الإلكتروني وسلامته ومصدره، ويوفّر ضمانات لحماية المواطنين من انتحال الهوية والتوقيع من دون صلاحية والتلاعب بالأسناد الرسمية. ويسهم كذلك في توحيد المعايير التقنية والإجرائية بين الإدارات العامة، بما يتيح تبادل الأسناد إلكترونياً بصورة آمنة وموثوقة.
+ويعزّز المرسوم المساءلة والشفافية من خلال اعتماد آليات لتتبّع المعاملات وسجلات للتحقق وأرشفة إلكترونية يمكن الرجوع إليها في عمليات التدقيق ومعالجة النزاعات. كما يلحظ تنفيذاً تدريجياً يراعي مستوى الجاهزية لدى كل إدارة، بالتوازي مع تطوير البنية الوطنية لخدمات الثقة.
+وفي هذا الإطار، ينظّم المرسوم التنسيق بين وزارة العدل ووزارة الدولة لشؤون التكنولوجيا والذكاء الاصطناعي ووزارة الدولة لشؤون التنمية الإدارية، ولا سيما في ما يتعلق بالتنفيذ وإطلاق المشاريع التجريبية وتدريب الموظفين، بما يضمن تكامل الجهود وتوحيد المقاربة المعتمدة في مختلف الإدارات العامة.
+وتؤكد الوزارتان أن إقرار هذا المرسوم يشكّل ثمرة للتعاون المؤسساتي بين الوزارات، وخطوة عملية نحو تحديث الإدارة العامة وتطوير الخدمات الحكومية، من خلال اعتماد حلول رقمية آمنة وموثوقة، وتعزيز كفاءة الإجراءات وشفافيتها، بما يضع احتياجات المواطنين في صلب مسار التحوّل الرقمي في لبنان.</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:28:28.139946+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/107/2</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>٢٩ تشرين الأول ، ٢٠٢٦ ١١:٢٨ ق.ظ
+EN
+FR
+عربي
+Toggle navigation
+الوزارة
+الوزير
+المدير العام
+عن الوزارة
+الهيكل التنظيمي
+الوزارة عبر التاريخ
+المؤتمرات
+سياسة التحديث
+مشاريع القوانين
+اتصل بنا
+خدمات المواطنين
+الخدمات
+قوانين مختارة
+نماذج إلكترونية
+الرسوم القضائية
+الخريطة القضائية
+دليل الأطباء الشرعيين
+دليل كتاب العدل
+دليل الخبراء المحلفين لدى المحاكم
+دليل المحامين
+الادارات
+حق الوصول الى المعلومات
+مصلحة الديوان
+مديرية شؤون القضاة والموظفين
+هيئة القضايا
+المديرية العامة
+مصلحة الطب الشرعي والأدلة الجنائية
+هيئة التشريع والاستشارات
+مركز المعلوماتية القضائية والقانونية
+صندوق تعاضد القضاة
+السجل التجاري
+معهد الدروس القضائية
+مصلحة إصلاح الأحداث المنحرفين
+مديرية السجون
+المحاكم
+المحاكم
+محاكم عدلية
+محاكم عسكرية
+القضاء الإداري
+ديوان المحاسبة
+التقسيمات الجغرافية للمحاكم
+احصائيات حول عمل المحاكم
+قضاء الملاحقة والتحقيق العادي
+إجراءات العمل القضائي
+مجلس القضاء الاعلى
+هيئة التفتيش القضائي
+التحكيم
+اتصل بنا
+أشخاص القطاع الحقوقي
+القضاة
+المحامون
+كتاب العدل
+الخبراء
+المساعدون القضائيون
+القضاة المتدرجون
+تصريح الإثراء غير المشروع
+التعاون الدولي
+أخبار ونشاطات
+إعلانات
+أرشيف الأخبار
+تجديد الإنتساب إلى جدول الخبراء ووكلاء التفليسة ومراقبي الصلح الاحتياطي
+٢٦ تشرين الأول ، ٢٠٢٦
+رجوع
+إعلان عن تجديد الانتساب
+إلى جدول الخبراء ووكلاء التفليسة ومراقبي الصلح الاحتياطي
+لكل من مضى على تاريخ انتسابه إلى الجدول أكثر من خمس سنوات
+عرض الإعلان
+طلب تجديد الإنتساب
+SELECT INTEREST
+النشرة الالكترونية
+إعلانات
+المنشورات القانونية
+عرض</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:28:36.393179+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/106/2</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>الصادرة عن رئيس هيئة الشراء العام بتاريخ 19/8/2022
+إسم الجهة الشارية
+وزارة العدل
+عنوان الجهة الشارية
+بيروت – المتحف – شارع سامي الصلح
+معلومات عن الصفقة
+رقم التسجيل
+108/هـ.ش.ع/2025
+عنوان الصفقة
+مناقصة عمومية لزوم تلزيم تأمين تجهيزات معلوماتية (المديرية العامة و المحاكم ) على اساس كل مجموعة على حدة
+وصف الصفقة
+مناقصة عمومية لزوم تلزيم تأمين تجهيزات معلوماتية (المديرية العامة و المحاكم ) على اساس كل مجموعة على حدة
+نوع التلزيم
+لوازم
+طريقة التلزيم
+مناقصة عمومية على اساس كل مجموعة على حدة
+ارساء التلزيم
+السعر الأدنى لكل مجموعة على حدة
+استخدام الإتفاق الإطاري
+لا ينطبق
+القيمة التقديرية للمشروع
+غير معلنة
+بدل دفتر الشروط
+لا يوجد
+لغات أخرى
+لا يوجد
+معايير وإجراءات
+تحدد المادة الثالثة والرابعة من ملف التلزيم المعايير والإجراءات التي تستخدم للتأكد من مؤهلات العارضين، ولأيّ أدلة مستندية أو معلومات أخرى يجب على العارضين أن يقدّموها لإثبات مؤهلاتهم وكذلك طريقة تقييم العروض.
+تواريخ/ مهل/ أماكن
+موعد جلسة التلزيم (فتح العروض)
+يوم الخميس الواقع في (15/10/2026) عند الساعة 11.00
+الموعد النهائي لتقديم العروض
+يوم الخميس الواقع في (15/10/2026) عند الساعة 10.30
+تخفيض مدة الإعلان
+21 يوماً
+الموعد النهائي لتقديم طلبات الاستيضاح
+يوم الاثنينالواقع في (5/10/2026)
+الموعد النهائي للرد على طلبات الاستيضاح
+يوم الجمعة الواقع في (9/10/2026)
+مدة صلاحية العرض
+/30/ يومًا من التاريخ النهائي لتقديم العروض
+مكان استلام دفتر الشروط
+وزارة العدل – الادارة المركزية – ط 5 – مصلحة الديوان
+مكان تقديم العروض
+وزارة العدل – الادارة المركزية – ط 5 – مصلحة الديوان
+مكان تقييم العروض
+وزارة العدل – الادارة المركزية – ط 1 – قاعة الاجتماعات
+ضمان العرض
+قيمة ضمان العرض
+يُحدد ضمان العرضبقيمة مقطوعة لكل مجموعة على حدة وفق اللائحة المرفقة
+مدة صلاحية ضمان العرض
+58 يوم من تاريخ تقديم العرض
+يمكنكم الإطلاع على دفتر الشروط الخاص بالصفقة عبر المنصة الإلكترونية المركزية لدى هيئة الشراء العام ppa.gov.lb
+ولمزيد من المعلومات يمكنكم في أي وقت مراجعة وحدة الشراء العام في الجهة الشارية عبر التواصل مع الديوان لدى وزارة العدل على الرقم التالي</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:28:42.952408+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/105/2</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>إعلان صادر عن دائرة السجل التجاري في جبل لبنان بشأن تتبّع أماكن وجود الملفات والحدّ من المراجعات لهذه الغاية.
+تُنشر أرقام الملفات المسحوبة من المبنى المُخلى ومواقع تخزينها، وتُحدَّث تباعًا عبر رابط Drive، بما يتيح لأصحاب العلاقة والسادة المحامين تتبّع ملفاتهم بسهولة من مكاتبهم أو منازلهم ومعرفة مكان وجودها، سواء في مستوعبات بعبدا، أو قاعة محكمة الجنايات في قصر عدل بعبدا، أو المبنى الجديد في جديدة، بدلًا من الانتقال إلى بعبدا لهذه الغاية، بما يحدّ من المراجعات غير الضرورية والاكتظاظ، علمًا أن الأرقام التي لا تظهر في رابط Drive تعود إلى ملفات لا تزال قيد السحب والنقل من المبنى المُخلى، ويعمل فريق العمل منذ بداية العطلة القضائية على إنجاز هذه العملية ونشر أرقام الملفات تباعًا على الرابط المذكور، في ظل جهود استثنائية تُبذل لتسهيل المراجعات وتسريع العمل، على أن يُنشر التحديث المقبل صباح يوم الاثنين 31/8/2026.
+لذلك، يُرجى من أصحاب العلاقة والسادة المحامين تتبّع ملفاتهم دوريًا والاطلاع على التحديثات المنشورة، مع التحقّق من وجود الملف في قاعة محكمة الجنايات في قصر عدل بعبدا قبل التوجّه إليها، تفاديًا للمراجعات غير المجدية وللشكاوى والتذمّر غير المبرّرين.
+رابط الإستعلام:
+https://drive.google.com/drive/folders/1t4bHhQthRQBz9WMFUivdi6E0eAM3ibwX?usp=drive_link  
+دليل مصوَر للبحث عن ملفات السجل التجاري</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:28:49.485341+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/103/2</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>٢٩ تشرين الأول ، ٢٠٢٦ ١١:٢٨ ق.ظ
+EN
+FR
+عربي
+Toggle navigation
+الوزارة
+الوزير
+المدير العام
+عن الوزارة
+الهيكل التنظيمي
+الوزارة عبر التاريخ
+المؤتمرات
+سياسة التحديث
+مشاريع القوانين
+اتصل بنا
+خدمات المواطنين
+الخدمات
+قوانين مختارة
+نماذج إلكترونية
+الرسوم القضائية
+الخريطة القضائية
+دليل الأطباء الشرعيين
+دليل كتاب العدل
+دليل الخبراء المحلفين لدى المحاكم
+دليل المحامين
+الادارات
+حق الوصول الى المعلومات
+مصلحة الديوان
+مديرية شؤون القضاة والموظفين
+هيئة القضايا
+المديرية العامة
+مصلحة الطب الشرعي والأدلة الجنائية
+هيئة التشريع والاستشارات
+مركز المعلوماتية القضائية والقانونية
+صندوق تعاضد القضاة
+السجل التجاري
+معهد الدروس القضائية
+مصلحة إصلاح الأحداث المنحرفين
+مديرية السجون
+المحاكم
+المحاكم
+محاكم عدلية
+محاكم عسكرية
+القضاء الإداري
+ديوان المحاسبة
+التقسيمات الجغرافية للمحاكم
+احصائيات حول عمل المحاكم
+قضاء الملاحقة والتحقيق العادي
+إجراءات العمل القضائي
+مجلس القضاء الاعلى
+هيئة التفتيش القضائي
+التحكيم
+اتصل بنا
+أشخاص القطاع الحقوقي
+القضاة
+المحامون
+كتاب العدل
+الخبراء
+المساعدون القضائيون
+القضاة المتدرجون
+تصريح الإثراء غير المشروع
+التعاون الدولي
+أخبار ونشاطات
+إعلانات
+أرشيف الأخبار
+قرار الغاء مناقصة المفروشات
+٠٧ تموز ، ٢٠٢٦
+رجوع
+تحميل الملف
+SELECT INTEREST
+النشرة الالكترونية
+إعلانات
+المنشورات القانونية
+عرض</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:28:56.021283+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/104/2</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>٢٩ تشرين الأول ، ٢٠٢٦ ١١:٢٨ ق.ظ
+EN
+FR
+عربي
+Toggle navigation
+الوزارة
+الوزير
+المدير العام
+عن الوزارة
+الهيكل التنظيمي
+الوزارة عبر التاريخ
+المؤتمرات
+سياسة التحديث
+مشاريع القوانين
+اتصل بنا
+خدمات المواطنين
+الخدمات
+قوانين مختارة
+نماذج إلكترونية
+الرسوم القضائية
+الخريطة القضائية
+دليل الأطباء الشرعيين
+دليل كتاب العدل
+دليل الخبراء المحلفين لدى المحاكم
+دليل المحامين
+الادارات
+حق الوصول الى المعلومات
+مصلحة الديوان
+مديرية شؤون القضاة والموظفين
+هيئة القضايا
+المديرية العامة
+مصلحة الطب الشرعي والأدلة الجنائية
+هيئة التشريع والاستشارات
+مركز المعلوماتية القضائية والقانونية
+صندوق تعاضد القضاة
+السجل التجاري
+معهد الدروس القضائية
+مصلحة إصلاح الأحداث المنحرفين
+مديرية السجون
+المحاكم
+المحاكم
+محاكم عدلية
+محاكم عسكرية
+القضاء الإداري
+ديوان المحاسبة
+التقسيمات الجغرافية للمحاكم
+احصائيات حول عمل المحاكم
+قضاء الملاحقة والتحقيق العادي
+إجراءات العمل القضائي
+مجلس القضاء الاعلى
+هيئة التفتيش القضائي
+التحكيم
+اتصل بنا
+أشخاص القطاع الحقوقي
+القضاة
+المحامون
+كتاب العدل
+الخبراء
+المساعدون القضائيون
+القضاة المتدرجون
+تصريح الإثراء غير المشروع
+التعاون الدولي
+أخبار ونشاطات
+إعلانات
+أرشيف الأخبار
+قرار قبول العرض الفائز المؤقت في مناقصة القرطاسية
+٠٧ تموز ، ٢٠٢٦
+رجوع
+SELECT INTEREST
+النشرة الالكترونية
+إعلانات
+المنشورات القانونية
+عرض</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:02.806095+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/102/2</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>يُعلن السجل التجاري في جبل لبنان لأصحاب العلاقة أنه يمكنهم، عبر الرابط الآتي، الاستعلام عن أماكن التخزين المؤقتة لملفاتهم المنقولة من المبنى المهدد بالسقوط،
+بما يحدّ من المراجعات غير الضرورية ويُيسّر متابعة معاملاتهم.
+https://drive.google.com/drive/folders/10NO8MYMUGcLDA2Nw5KuGo_FTnWdZTB-j?usp=drive_link</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:09.225261+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/101/2</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>٢٩ تشرين الأول ، ٢٠٢٦ ١١:٢٩ ق.ظ
+EN
+FR
+عربي
+Toggle navigation
+الوزارة
+الوزير
+المدير العام
+عن الوزارة
+الهيكل التنظيمي
+الوزارة عبر التاريخ
+المؤتمرات
+سياسة التحديث
+مشاريع القوانين
+اتصل بنا
+خدمات المواطنين
+الخدمات
+قوانين مختارة
+نماذج إلكترونية
+الرسوم القضائية
+الخريطة القضائية
+دليل الأطباء الشرعيين
+دليل كتاب العدل
+دليل الخبراء المحلفين لدى المحاكم
+دليل المحامين
+الادارات
+حق الوصول الى المعلومات
+مصلحة الديوان
+مديرية شؤون القضاة والموظفين
+هيئة القضايا
+المديرية العامة
+مصلحة الطب الشرعي والأدلة الجنائية
+هيئة التشريع والاستشارات
+مركز المعلوماتية القضائية والقانونية
+صندوق تعاضد القضاة
+السجل التجاري
+معهد الدروس القضائية
+مصلحة إصلاح الأحداث المنحرفين
+مديرية السجون
+المحاكم
+المحاكم
+محاكم عدلية
+محاكم عسكرية
+القضاء الإداري
+ديوان المحاسبة
+التقسيمات الجغرافية للمحاكم
+احصائيات حول عمل المحاكم
+قضاء الملاحقة والتحقيق العادي
+إجراءات العمل القضائي
+مجلس القضاء الاعلى
+هيئة التفتيش القضائي
+التحكيم
+اتصل بنا
+أشخاص القطاع الحقوقي
+القضاة
+المحامون
+كتاب العدل
+الخبراء
+المساعدون القضائيون
+القضاة المتدرجون
+تصريح الإثراء غير المشروع
+التعاون الدولي
+أخبار ونشاطات
+إعلانات
+أرشيف الأخبار
+ابلاغ بوجوب توقيع عقد اتفاف أعمال التنظيفات
+١٧ حزيران ، ٢٠٢٦
+رجوع
+SELECT INTEREST
+النشرة الالكترونية
+إعلانات
+المنشورات القانونية
+عرض</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:16.222193+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/100/2</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>٢٩ تشرين الأول ، ٢٠٢٦ ١١:٢٩ ق.ظ
+EN
+FR
+عربي
+Toggle navigation
+الوزارة
+الوزير
+المدير العام
+عن الوزارة
+الهيكل التنظيمي
+الوزارة عبر التاريخ
+المؤتمرات
+سياسة التحديث
+مشاريع القوانين
+اتصل بنا
+خدمات المواطنين
+الخدمات
+قوانين مختارة
+نماذج إلكترونية
+الرسوم القضائية
+الخريطة القضائية
+دليل الأطباء الشرعيين
+دليل كتاب العدل
+دليل الخبراء المحلفين لدى المحاكم
+دليل المحامين
+الادارات
+حق الوصول الى المعلومات
+مصلحة الديوان
+مديرية شؤون القضاة والموظفين
+هيئة القضايا
+المديرية العامة
+مصلحة الطب الشرعي والأدلة الجنائية
+هيئة التشريع والاستشارات
+مركز المعلوماتية القضائية والقانونية
+صندوق تعاضد القضاة
+السجل التجاري
+معهد الدروس القضائية
+مصلحة إصلاح الأحداث المنحرفين
+مديرية السجون
+المحاكم
+المحاكم
+محاكم عدلية
+محاكم عسكرية
+القضاء الإداري
+ديوان المحاسبة
+التقسيمات الجغرافية للمحاكم
+احصائيات حول عمل المحاكم
+قضاء الملاحقة والتحقيق العادي
+إجراءات العمل القضائي
+مجلس القضاء الاعلى
+هيئة التفتيش القضائي
+التحكيم
+اتصل بنا
+أشخاص القطاع الحقوقي
+القضاة
+المحامون
+كتاب العدل
+الخبراء
+المساعدون القضائيون
+القضاة المتدرجون
+تصريح الإثراء غير المشروع
+التعاون الدولي
+أخبار ونشاطات
+إعلانات
+أرشيف الأخبار
+مناقصة عمومية لتلزيم تأمين قرطاسية لزوم وزارة العدل (المديرية العامة والمحاكم) - معدل
+٠٣ حزيران ، ٢٠٢٦
+رجوع
+دعوة للإعلان عن مناقصة عمومية
+عملًا بالمذكرة رقم 4/
+ه
+.ش.ع/2022
+الصادرة عن رئيس هيئة الشراء العام بتاريخ 19/8/2022
+إسم الجهة الشارية
+وزارة العدل
+عنوان الجهة الشارية
+بيروت – المتحف – شارع سامي الصلح
+معلومات عن الصفقة
+رقم التسجيل
+244/هـ.ش.ع/2025
+عنوان الصفقة
+مناقصة عمومية لزوم تلزيم تأمين قرطاسية لزوم وزارة الـعـدل (المديرية العامة و المحاكم ) على اساس كل مجموعة على حدة
+وصف الصفقة
+مناقصة عمومية لزوم تلزيم تأمين قرطاسية لزوم وزارة الـعـدل (المديرية العامة و المحاكم ) على اساس كل مجموعة على حدة
+نوع التلزيم
+لوازم
+طريقة
+التلزيم
+مناقصة عمومية على اساس كل مجموعة على حدة
+ارساء التلزيم
+السعر الأدنى
+لكل مجموعة على حدة
+استخدام الإتفاق الإطاري
+لا ينطبق
+القيمة التقديرية للمشروع
+غير معلنة
+بدل دفتر الشروط
+لا يوجد
+لغات أخرى
+لا يوجد
+معايير وإجراءات
+تحدد المادة الثالثة والرابعة من ملف التلزيم المعايير والإجراءات التي تستخدم للتأكد من مؤهلات العارضين، ولأيّ أدلة مستندية أو معلومات أخرى يجب على العارضين أن يقدّموها لإثبات مؤهلاتهم وكذلك طريقة تقييم العروض.
+تواريخ/ مهل/ أماكن
+موعد جلسة التلزيم (فتح العروض)
+يوم الخميس الواقع في (25/6/2026) عند الساعة 11.00
+الموعد النهائي لتقديم العروض
+يوم الخميس الواقع في (25/6/2026) عند الساعة 10.30
+تخفيض مدة الإعلان
+21 يوماً
+الموعد النهائ
+ي لتقديم
+طلبات الاستيضاح
+يوم الاثنين الواقع في (15/6/2026)
+الموعد النهائي للرد على طلبات الاستيضاح
+يوم االجمعة الواقع في (19/6/2026)
+مدة صلاحية العرض
+/30/ يومًا من التاريخ النهائي لتقديم العروض
+مكان استلام دفتر الشروط
+وزارة العدل – الادارة المركزية – ط 5 – مصلحة الديوان
+مكان تقديم العروض
+وزارة العدل – الادارة المركزية – ط 5 – مصلحة الديوان
+مكان تقييم العروض
+وزارة العدل – الادارة المركزية – ط 1 – قاعة الاجتماعات
+ضمان العرض
+قيمة ضمان العرض
+يُحدد ضمان العرضبقيمة مقطوعة لكل مجموعة على حدة وفق اللائحة المرفقة
+مدة صلاحية ضمان العرض
+58 يوم من تاريخ تقديم العرض
+يمكنكم الإطلاع على دفتر الشروط الخاص بالصفقة عبر المنص
+ة
+الإلكترونية المركزية لدى هيئة الشراء العام
+ppa.gov.lb
+ولمزيد من المعلومات يمكنكم في أي وقت مراجعة وحدة الشراء العام في الجهة الشارية عبر التواصل مع الديوان لدى وزارة العدل على الرقم التالي
+612573/01
+-
+398369/01
+تحميل الملف
+SELECT INTEREST
+النشرة الالكترونية
+إعلانات
+المنشورات القانونية
+عرض</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:22.738536+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/99/2</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>٢٩ تشرين الأول ، ٢٠٢٦ ١١:٢٩ ق.ظ
+EN
+FR
+عربي
+Toggle navigation
+الوزارة
+الوزير
+المدير العام
+عن الوزارة
+الهيكل التنظيمي
+الوزارة عبر التاريخ
+المؤتمرات
+سياسة التحديث
+مشاريع القوانين
+اتصل بنا
+خدمات المواطنين
+الخدمات
+قوانين مختارة
+نماذج إلكترونية
+الرسوم القضائية
+الخريطة القضائية
+دليل الأطباء الشرعيين
+دليل كتاب العدل
+دليل الخبراء المحلفين لدى المحاكم
+دليل المحامين
+الادارات
+حق الوصول الى المعلومات
+مصلحة الديوان
+مديرية شؤون القضاة والموظفين
+هيئة القضايا
+المديرية العامة
+مصلحة الطب الشرعي والأدلة الجنائية
+هيئة التشريع والاستشارات
+مركز المعلوماتية القضائية والقانونية
+صندوق تعاضد القضاة
+السجل التجاري
+معهد الدروس القضائية
+مصلحة إصلاح الأحداث المنحرفين
+مديرية السجون
+المحاكم
+المحاكم
+محاكم عدلية
+محاكم عسكرية
+القضاء الإداري
+ديوان المحاسبة
+التقسيمات الجغرافية للمحاكم
+احصائيات حول عمل المحاكم
+قضاء الملاحقة والتحقيق العادي
+إجراءات العمل القضائي
+مجلس القضاء الاعلى
+هيئة التفتيش القضائي
+التحكيم
+اتصل بنا
+أشخاص القطاع الحقوقي
+القضاة
+المحامون
+كتاب العدل
+الخبراء
+المساعدون القضائيون
+القضاة المتدرجون
+تصريح الإثراء غير المشروع
+التعاون الدولي
+أخبار ونشاطات
+إعلانات
+أرشيف الأخبار
+مناقصة عمومية لتلزيم مفروشات لصالح وزارة الـعـدل (المحاكم)
+١٨ أيّار ، ٢٠٢٦
+رجوع
+دعوة للإعلان عن مناقصة عمومية
+عملًا بالمذكرة رقم 4/
+ه
+.ش.ع/2022
+الصادرة عن رئيس هيئة الشراء العام بتاريخ 19/8/2022
+إسم الجهة الشارية
+وزارة العدل
+عنوان الجهة الشارية
+بيروت – المتحف – شارع سامي الصلح
+معلومات عن الصفقة
+رقم التسجيل
+271/هـ.ش.ع/2026
+عنوان الصفقة
+مناقصة عمومية لزوم تلزيم مفروشات لصالح وزارة الـعـدل (المحاكم ) على اساس كل صنف على حدة
+وصف الصفقة
+مناقصة عمومية لزوم تلزيم مفروشات لصالح وزارة الـعـدل (المحاكم ) على اساس كل صنف على حدة
+نوع التلزيم
+لوازم
+طريقة
+التلزيم
+مناقصة عمومية على اساس كل صنف على حدة
+ارساء التلزيم
+السعر الأدنى
+لكل صنف على حدة
+استخدام الإتفاق الإطاري
+لا ينطبق
+القيمة التقديرية للمشروع
+غير معلنة
+بدل دفتر الشروط
+لا يوجد
+لغات أخرى
+لا يوجد
+معايير وإجراءات
+تحدد المادة الثالثة والرابعة من ملف التلزيم المعايير والإجراءات التي تستخدم للتأكد من مؤهلات العارضين، ولأيّ أدلة مستندية أو معلومات أخرى يجب على العارضين أن يقدّموها لإثبات مؤهلاتهم وكذلك طريقة تقييم العروض.
+تواريخ/ مهل/ أماكن
+موعد جلسة التلزيم (فتح العروض)
+يوم الاربعاء الواقع في (24/6/2026) عند الساعة 11.00
+الموعد النهائي لتقديم العروض
+يوم الاربعاء الواقع في (24/6/2026) عند الساعة 10.30
+تخفيض مدة الإعلان
+21 يوماً
+الموعد النهائ
+ي لتقديم
+طلبات الاستيضاح
+يوم الجمعة الواقع في (12/6/2026)
+الموعد النهائي للرد على طلبات الاستيضاح
+يوم الاثنين الواقع في (15/6/2026)
+مدة صلاحية العرض
+/30/ يومًا من التاريخ النهائي لتقديم العروض
+مكان استلام دفتر الشروط
+وزارة العدل – الادارة المركزية – ط 5 – مصلحة الديوان
+مكان تقديم العروض
+وزارة العدل – الادارة المركزية – ط 5 – مصلحة الديوان
+مكان تقييم العروض
+وزارة العدل – الادارة المركزية – ط 1 – قاعة الاجتماعات
+ضمان العرض
+قيمة ضمان العرض
+يُحدد ضمان العرضبقيمة مقطوعة لكل صنف على حدة وفق اللائحة المرفقة
+مدة صلاحية ضمان العرض
+58 يوم من تاريخ تقديم العرض
+يمكنكم الإطلاع على دفتر الشروط الخاص بالصفقة عبر المنص
+ة
+الإلكترونية المركزية لدى هيئة الشراء العام
+ppa.gov.lb
+ولمزيد من المعلومات يمكنكم في أي وقت مراجعة وحدة الشراء العام في الجهة الشارية عبر التواصل مع الديوان لدى وزارة العدل على الرقم التالي
+612573/01
+-
+398369/01
+تحميل الملف
+SELECT INTEREST
+النشرة الالكترونية
+إعلانات
+المنشورات القانونية
+عرض</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:29.591801+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/89/2</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>٢٩ تشرين الأول ، ٢٠٢٦ ١١:٢٩ ق.ظ
+دعوة للإعلان عن مناقصة عمومية
+عملًا بالمذكرة رقم 4/ه.ش.ع/2022
+الصادرة عن رئيس هيئة الشراء العام بتاريخ 19/8/2022
+إسم الجهة الشارية
+وزارة العدل
+عنوان الجهة الشارية
+بيروت – المتحف – شارع سامي الصلح
+معلومات عن الصفقة
+رقم التسجيل
+212/هـ.ش.ع/2025
+عنوان الصفقة
+مناقصة عمومية لزوم تلزيم تأمين مطبوعات لزوم وزارة الـعـدل (المديرية العامة و المحاكم ) على اساس كل مجموعة على حدة
+وصف الصفقة
+نوع التلزيم
+لوازم
+طريقة التلزيم
+مناقصة عمومية على اساس كل مجموعة على حدة
+ارساء التلزيم
+السعر الأدنى لكل مجموعة على حدة
+استخدام الإتفاق الإطاري
+لا ينطبق
+القيمة التقديرية للمشروع
+غير معلنة
+بدل دفتر الشروط
+لا يوجد
+لغات أخرى
+لا يوجد
+معايير وإجراءات
+تحدد المادة الثالثة والرابعة من ملف التلزيم المعايير والإجراءات التي تستخدم للتأكد من مؤهلات العارضين، ولأيّ أدلة مستندية أو معلومات أخرى يجب على العارضين أن يقدّموها لإثبات مؤهلاتهم وكذلك طريقة تقييم العروض.
+تواريخ/ مهل/ أماكن
+موعد جلسة التلزيم (فتح العروض)
+يوم الاثنين الواقع في (11/5/2026) عند الساعة 11.00
+الموعد النهائي لتقديم العروض
+يوم االاثنين الواقع في (11/5/2026) عند الساعة 10.30
+تخفيض مدة الإعلان
+21 يوماً
+الموعد النهائي لتقديم طلبات الاستيضاح
+يوم الاثنين الواقع في (27/4/2026)
+الموعد النهائي للرد على طلبات الاستيضاح
+يوم الجمعة الواقع في (1/5/2026)
+مدة صلاحية العرض
+/30/ يومًا من التاريخ النهائي لتقديم العروض
+مكان استلام دفتر الشروط
+وزارة العدل – الادارة المركزية – ط 5 – مصلحة الديوان
+مكان تقديم العروض
+مكان تقييم العروض
+وزارة العدل – الادارة المركزية – ط 1 – قاعة الاجتماعات
+ضمان العرض
+قيمة ضمان العرض
+يُحدد ضمان العرض بقيمة مقطوعة لكل مجموعة على حدة وفق اللائحة المرفقة
+مدة صلاحية ضمان العرض
+58 يوم من تاريخ تقديم العرض
+يمكنكم الإطلاع على دفتر الشروط الخاص بالصفقة عبر المنصة الإلكترونية المركزية لدى هيئة الشراء العام ppa.gov.lb
+ولمزيد من المعلومات يمكنكم في أي وقت مراجعة وحدة الشراء العام في الجهة الشارية عبر التواصل مع الديوان لدى وزارة العدل على الرقم التالي
+612573/01 - 398369/01
+SELECT INTEREST
+النشرة الالكترونية
+إعلانات
+المنشورات القانونية</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:36.767794+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/88/2</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>نظراً للاوضاع الامنية الراهنة فقد تقرر تأجيل موعد استقبال العروض الى يوم الخميس 30 نيسسان 2026 الساعة 11:00 صباحاٌ في وزارة العدل، مصلحة الديوان، الطابق الخامس.
+تُجري وزارة العدل استدراج عروض لمشتريات بالفاتورة لمصلحة المديرية العامة والمحاكم.
+تجدون العروض مرفقة مع هذا الإعلان.
+يتم استقبال العروض لغاية الخميس 16 نيسان 2026 الساعة 12 ظهراً في وزارة العدل، مصلحة الديوان، الطابق الخامس.
+للإستفسار: [email protected]
+تحميل العروض:</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:39.173097+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/announcement-details/84/2</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>٢٩ تشرين الأول ، ٢٠٢٦ ١١:٢٩ ق.ظ
+مناقصة عمومية/ لتلزيم أعمال تنظيف الإدارة المركزية لوزارة العدل(ثلاث مبانٍ)
+وقصور العدل في بيروت –
+بعبدا (مبنيين)-جديدة المتن- زحلة – صيدا – النبطية – بعلبك – طرابلس
+وملحقات قصور العدل في المحافظات
+(المحاكم المنفردة)
+مُلخّص عن الصفقة
+إسم الجهة الشارية
+وزارة العدل
+عنوان الجهة الشارية
+بيروت – المتحف – شارع سامي الصلح
+رقم وتاريخ التسجيل
+عنوان الصفقة
+تلزيم اعمال تنظيف الادارة المركزية لوزارة العدل والمباني التابعة لها وقصور العدل وملحقاتها في المحافظات كافة . على اساس كل مبنى على حدة
+موضوع الصفقة
+مناقصة عمومية لزوم تلزيم اعمال تنظيف الادارة المركزية لوزارة العدل والمباني التابعة لها وقصور العدل وملحقاتها في المحافظات كافة.على اساس كل مبنى على حدة
+طريقة التلزيم
+مناقصة عمومية على اساس تقديم اسعار لكل مبنى
+نوع التلزيم
+خدمات
+مدة صلاحية العرض
+/30/ يوماً من التاريخ النهائي لتقديم العروض
+ضمان العرض
+يُحدد ضمان العرض بقيمة مقطوعة لكل مبنى على حدة وفق اللائحة المرفقة
+مدة صلاحية ضمان العرض
+58 يوماً من تاريخ تقديم العرض
+ضمان حسن التنفيذ
+10% من قيمة العقد.
+الإرساء
+السعر الأدنى لكل مبنى على حدة
+معاينة الموقع
+ايام الاثنين ، الثلاثاء والاربعاء من كل اسبوع بين الساعة التاسعة والواحدة ظهرا من كل اسبوع .
+مكان استلام دفتر الشروط
+وزارة العدل – الادارة المركزية – ط 5 – مصلحة الديوان
+مكان تقديم العروض
+مكان تقييم العروض
+وزارة العدل – الادارة المركزية – ط 1 – قاعة الاجتماعات
+مدة التنفيذ
+سنة واحدة قابلة للتمديد لمدة ثلاث سنوات متتالية
+عملة العقد
+الليرة اللبنانية
+دفع قيمة العقد
+شهريا ولمدة اثنا عشر شهرا
+SELECT INTEREST
+النشرة الالكترونية
+إعلانات
+المنشورات القانونية</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:45.732212+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/news-details/1456/2</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>أعلنت وزارة العدل ووزارة الدولة لشؤون التكنولوجيا والذكاء الاصطناعي موافقة مجلس الوزراء على مشروع المرسوم التطبيقي لتنظيم الأسناد الرسمية الإلكترونية والتوقيع الإلكتروني، الذي أعدّته وزارة العدل بالتعاون مع وزارة الدولة لشؤون التكنولوجيا والذكاء الاصطناعي، في خطوة أساسية نحو تفعيل الإطار القانوني للتحوّل الرقمي في الإدارات العامة وتعزيز موثوقية المعاملات الإلكترونية.
+ويلغي المرسوم الجديد صراحةً المرسومين رقم 14115/2024 ورقم 14555/2025، ويعتمد إطاراً تنفيذياً مرحلياً يتيح للإدارات العامة البدء بتطبيق أحكامه من دون انتظار اكتمال البنية الوطنية للاعتماد، وفق المعايير التقنية المعتمدة في التنظيم الأوروبي eIDAS، مع ضمان توطين العناصر الجوهرية لخدمات الثقة على الأراضي اللبنانية.
+ويهدف المرسوم إلى وضع أحكام القانون رقم 81/2018 موضع التطبيق الفعلي، من خلال توفير إطار واضح لإنشاء الأسناد الرسمية الإلكترونية وتوقيعها وتبادلها وحفظها، بما يتيح تقليص الاعتماد على المعاملات الورقية، والحد من التأخير والكلفة، وتخفيف حاجة المواطنين إلى الحضور الشخصي لإنجاز معاملاتهم.
+كما يحدّد المرسوم شروط التحقق من صحة السند الإلكتروني وسلامته ومصدره، ويوفّر ضمانات لحماية المواطنين من انتحال الهوية والتوقيع من دون صلاحية والتلاعب بالأسناد الرسمية. ويسهم كذلك في توحيد المعايير التقنية والإجرائية بين الإدارات العامة، بما يتيح تبادل الأسناد إلكترونياً بصورة آمنة وموثوقة.
+ويعزّز المرسوم المساءلة والشفافية من خلال اعتماد آليات لتتبّع المعاملات وسجلات للتحقق وأرشفة إلكترونية يمكن الرجوع إليها في عمليات التدقيق ومعالجة النزاعات. كما يلحظ تنفيذاً تدريجياً يراعي مستوى الجاهزية لدى كل إدارة، بالتوازي مع تطوير البنية الوطنية لخدمات الثقة.
+وفي هذا الإطار، ينظّم المرسوم التنسيق بين وزارة العدل ووزارة الدولة لشؤون التكنولوجيا والذكاء الاصطناعي ووزارة الدولة لشؤون التنمية الإدارية، ولا سيما في ما يتعلق بالتنفيذ وإطلاق المشاريع التجريبية وتدريب الموظفين، بما يضمن تكامل الجهود وتوحيد المقاربة المعتمدة في مختلف الإدارات العامة.
+وتؤكد الوزارتان أن إقرار هذا المرسوم يشكّل ثمرة للتعاون المؤسساتي بين الوزارات، وخطوة عملية نحو تحديث الإدارة العامة وتطوير الخدمات الحكومية، من خلال اعتماد حلول رقمية آمنة وموثوقة، وتعزيز كفاءة الإجراءات وشفافيتها، بما يضع احتياجات المواطنين في صلب مسار التحوّل الرقمي في لبنان.</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:47.763769+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/news-details/1455/2</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>تحت رعاية وزارة العدل اللبنانية، وبالتعاون مع نقابة المحامين في بيروت والشريك المحلي بيريتك، وبدعم من وزارة الخارجية الهولندية، اختُتمت في بيروت أمس الأحد 11 تشرين الأول فعاليات «هاكاثون لبنان للعدالة 2026»، الذي نظّمه معهد لاهاي للابتكار القانوني (HiiL).
+جمع الهاكاثون 16 فريقاً ضمّت 64 مشاركاً من مجالات القانون، والتكنولوجيا، والذكاء الاصطناعي، والتصميم، وريادة الأعمال، والبحث، والخدمة العامة. وعلى مدى يومين، عملت الفرق على تحدٍّ واقعي في قطاع العدالة تم تحديده بالتعاون مع وزارة العدل، بهدف تطوير نماذج أولية عملية تساعد على تحسين تجربة مستخدمي المحاكم وتسهيل الوصول إلى المعلومات والإرشادات الأساسية. وركّز التحدّي على تمكينهم من متابعة ملفاتهم، ومعرفة المراحل التي بلغتها والإجراءات المطلوبة منهم، في ظل عدم مكننة المحاكم، بما يحدّ من الاستفسارات والمراجعات المتكررة ويخفّف الأعباء عن موظفي أقلام المحاكم.
+وافتُتح الهاكاثون بكلمة السيد روجيه الخوري، مدير برامج الشرق الأوسط وشمال أفريقيا لدى معهد لاهاي للابتكار القانوني (HiiL)، تلتها كلمة السيد مارون شمّاس، رئيس مجلس الإدارة والرئيس التنفيذي لبيريتك، ثم كلمة راعي الهاكاثون، وزير العدل عادل نصار الذي اعرب عن تقديره لهولندا لدعمهاالمتواصل لقطاع العدالة في لبنان، مشيدا بالمشاريع التي تساهم في تطوير هذا القطاع، ولا سيما المبادرات الهادفة إلى تعزيز التواصل بين القضاء والرأي العام، ودعم معهد الدروس القضائية وتوفير برامج تدريبية للقضاة.
+وأيضاً أكد الوزير نصار على أهمية المبادرات التي تجمع التكنولوجيا والعدالة، معتبراً أن الاهتمام الذي يحظى به هذا المجال في لبنان يشكّل فرصة لتطوير الخدمات القانونية وتسهيل وصول المواطنين إلى حقوقهم مشيراً إلى أن ثمة فرقاً بين تنظيم المجتمع وتحقيق العدالة، موضحاً أن القانون يهدف إلى تنظيم العلاقات بين الأفراد، لكن وجود القوانين لا يعني بالضرورة أن جميع المواطنين يتمتعون بقدرة متساوية على الاستفادة منها أو المطالبة بحقوقهم.ولفت في هذا السياق إلى أن المساواة أمام القانون لا تعني بالضرورة توافر الإمكانات نفسها لدى الجميع، إذ تختلف القدرات العلمية والمادية بين المواطنين ، كما استشهد نصار بمقولة للكاتب جورج أورويل مفادها أن جميع الناس متساوون، لكن بعضهم أكثر مساواة من الآخرين، في إشارة إلى الفجوة بين المساواة النظرية والواقع العملي...وشدد على أن عدم معرفة المواطن بحقوقه، أو عجزه عن تحمّل تكاليف المحاماة والتقاضي، قد يحولان دون حصوله على العدالة. ومن هنا تبرز مسؤولية الدولة والمؤسسات المعنية في نشر الثقافة القانونية، وتعريف المواطنين بحقوقهم، ومساعدتهم على الوصول إلى الجهات القادرة على تقديم الدعم اللازم.
+وأوضح أن المبادرات القائمة تسعى إلى جمع الجمعيات والمؤسسات ونقابة المحامين ضمن إطار تعاوني يتيح الاستفادة من الإمكانات المتوافرة، وتوجيه الأشخاص الذين يحتاجون إلى مساعدة قانونية نحو الجهات المناسبة، سواء للحصول على الاستشارات أو التمثيل القانوني أو المساعدة في متابعة الإجراءات القضائية.
+وفي هذا الإطار، تبرز أهمية إنشاء منصة موحّدة تجمع المعلومات المتعلقة بالخدمات التي تقدمها المؤسسات والجمعيات المعنية، بما يسهّل على المواطنين معرفة الجهات التي يمكنها مساعدتهم، ويعزز التنسيق بين مقدمي هذه الخدمات، ويحدّ من تشتت الجهود.
+وأكد أن الهدف من إدخال التكنولوجيا إلى قطاع العدالة ليس استبدال المحامين أو الانتقاص من دورهم الأساسي في الدفاع عن موكليهم وتمثيلهم أمام المحاكم، بل توسيع نطاق الوصول إلى المعلومات والخدمات القانونية، ولا سيما بالنسبة إلى الفئات التي تواجه صعوبات مالية تحول دون حصولها عليها.
+واذ اكد على أن توظيف التكنولوجيا بصورة مدروسة، بالتوازي مع التعاون بين الدولة والمؤسسات المهنية والجمعيات ضروري جدا لمساعدة المواطن ودعمه ،اعتبر الوزير ان وصول الريموت كونترول قلب المقاييس واجبر المحطات التلفزيونية على تطوير برامجها لابقاء المواطن أمام شاشة معينة،وخلق سرعة في التطوير والمعلومات وهذا ما أثر بشكل كبير على المجتمعات ،اما الذكاء الاصطناعي فسيكون له تأثير أكبر بكثير لانه سينقلنا الى عالم آخر لا نعرف تفاصيله بعد وفي كل المجالات .
+وأضاف مشددا على أنه في القانون الامر مختلف لان لدينا نقطة أساسية وهي المحافظة على تنظيم المجتمع على اساس مبدأ ،ان من يضع القوانين هو الانسان الذي لديهم اخطاءه وصعوبات وعليه ان ينظم اشخاصا لديهم صعوباتهم واخطائهم ،من هنا علينا ان نحافظ على البعد الانساني فيه وهذا هو الجوهر ،وإذا تجاهلنا هذا الامر نصبح في مكان خطير ،علينا ان لا نستبدل الإنسان وانساني بالذكاء الاصطناعي بل ان على التكنولوجيا والذكاء الاصطناعي ان تدعم عمل الإنسان.
+وختم بالقول
+"ان عملكم اساسي لتحقيق هذا الهدف خصوصا وانه من صلب عمل الوزارة لاننا نعمل في الوزارة على ضم كل العاملين الى هذا المجال للوصول الى العدالة وهو ما ستساهمون به الى حد كبير لمساعدة كل الاشخاص للوصول الى حياة افضل .
+بعدها كانت كلمة لنقيب المحامين في بيروت الأستاذ عماد مارتينوس، من ثم كلمة السيدة ماريكا ڤيردا، نائبة سفير مملكة هولندا لدى لبنان، فيما أكدت الكلمات على أهمية التعاون بين المؤسسات العامة والعاملين في المجالات القانونية والتكنولوجية والابتكارية لتطوير حلول عملية تُسهم في تعزيز العدالة المتمحورة حول الإنسان في لبنان.
+ويأتي الهاكاثون ضمن برنامج يمتدّ لخمس سنوات ينفّذه معهد لاهاي للابتكار القانوني في لبنان، بدعم من وزارة الخارجية الهولندية وبالتعاون مع الشركاء المحليين، لتعزيز الابتكار في قطاع العدالة وتطوير حلول تستجيب لاحتياجات الناس.
+هذا وقد قدّمت الفرق حلولها أمام لجنة تحكيم ضمّت خبراء وممثلين من قطاعات العدالة، والتكنولوجيا، والابتكار، والتصميم، والتنفيذ العملي. وقيّمت اللجنة النماذج الأولية بناءً على ارتباطها بالتحدّي، وفهمها لاحتياجات المستخدمين، وقابليتها للتنفيذ، واحترامها للضوابط القانونية والعملية، ومدى وضوح النموذج الأولي وإمكانية تجربته.
+وفي ختام الهاكاثون، أُعلنت الفرق الفائزة على النحو الآتي:
+● المركز الأول: فريق «Access to Digital Law» عن مشروع «دليل»: وهو نموذج أولي يساعد المواطنين، قبل التوجّه إلى المحكمة، على معرفة المستندات والرسوم والخطوات المطلوبة، ويمكّنهم، بعد تقديم الملف، من تلقّي تحديثات عبر الرسائل القصيرة بشأن سير الملف والخطوة التالية، استنادًا إلى ما يسجّله موظّفو الأقلام، بما يسهم في تقليل المراجعات المتكرّرة وتخفيف العبء عنهم.
+● المركز الثاني: «LexDarb961»: وهو تطبيق متكامل يقدّم أربع خدمات مترابطة: مساعدة المواطنين على معرفة المستندات المطلوبة ومتابعة حالة معاملاتهم والخطوات التالية، وتمكين موظفي أقلام المحاكم من تحديث حالة المستندات بخطوات بسيطة وسريعة، وتوفير قسم مخصّص للمحامين، ومساعد صوتي ذكي للتوجيه.
+● المركز الثالث: «Nobel Lex» عن مشروع «دليلك للمحاكم المدنية» ويهدف المشروع إلى توفير معلومات إجرائية واضحة وموثوقة حول معاملات المحاكم المدنية عبر موقع وزارة العدل، بما يساعد المواطنين والحقوقيين على فهم الخطوات المطلوبة، ويخفّف عبء الاستفسارات المتكررة على موظفي المحاكم.
+وحصلت الفرق الفائزة على جوائز بقيمة إجمالية بلغت 9,000 يورو، موزعة على 5,000 يورو للمركز الأول، و3,000 يورو للمركز الثاني، و1,000 يورو للمركز الثالث.
+وفي ختام «هاكاثون لبنان للعدالة 2026»، جدّد معهد لاهاي للابتكار القانوني ووزارة خارجية مملكة هولندا، الجهة الداعمة له، التزامهما بمواصلة العمل المشترك مع وزارة العدل اللبنانية ونقابة المحامين والشركاء المحليين لدعم قطاع العدالة في لبنان.</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:49.839055+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/news-details/11/2</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>افتتحت في القاهرة اليوم اعمال اجتماع مجلس وزراء العدل العرب الذي عقد في مقر الجامعة العربية، وترأس وزير العدل المستقيل اللواء اشرف ريفي وفد لبنان الى المؤتمر الذي ضم الى ريفي، السفير عبد الرحمن الصلح مدير المركز العربي للشؤون القانونية والقضائية وجوزيف رحمة أحد كبار موظفي المركز.
+وقد ناقش المؤتمر القضايا المتعلقة بجدول الاعمال، واستهل بكلمة لوزير العدل الأردني الرئيس السابق لمجلس وزراء العدل العرب . وبعد ذلك تمَّ تسليم رئاسة المجلس لوزير العدل العراقي الدكتور حيدر الزاملي الذي إفتتح الدورة الحالية وهي الدورة 32 للمجلس .
+ثم كانت كلمة للرئيس الفخري للمجلس ، وزير العدل السعودي الشيخ الدكتور وليد بن محمد الصمعاني الذي ألقى كلمة المملكة العربية السعودية.
+وأُقرّ جدول أعمال الجلسة وتمَّ إستعراض بنود الدورة تباعاً ، وكان للوزير ريفي مداخلات عدة تعقيباً وإقتراحاً للمواضيع المطروحة، حيث اقترح تغيير موعد تعيين اليوم العربي لمكافحة الفساد، من 25 كانون الاول الى موعد لاحق باعتباره يصادف عيد ميلاد السيد المسيح عليه السلام ، وأقر المشاركون تغيير الموعد، بناء على الاقتراح.. وفي موضوع قيام العدو الاسرائيلي بتحضير مشروع قانون لمنع الآذان في القدس المحتلة،إقترح ريفي أن يتضمن البيان الختامي للمجلس إدانة لما يقوم به العدو الإسرائيلي من منعٍ للآذان في مدينة القدس، وأبلغ المجتمعين أن بيروت هي مدينة العيش المشترك وأنها أدانت السلوك الإسرائيلي من خلال مشاركة أصوات أجراس الكنائس لآذان المساجد في توقيتٍ واحد.
+وقد أقر المؤتمر في اليوم الأول مجموعة من القرارات اهمها:
+    - قرار بتحديث الإتفاقية العربية لمكافحة الإرهاب وآلية تنفيذها
+- قرار بتحديث الإتفاقية العربية لمكافحة غسل الأموال وتمويل الإرهاب
+- قرار بشأن تجريم دفع الفدية
+- قرار بتعديل القانون العربي الموحَّد النموذجي للمخدرات والمؤثرات العقلية
+- قرار بشأن مشروع قانون عربي إسترشادي لمساعدة ضحايا الأعمال الإرهابية
+- قرار بشأن الإتفاقية العربية لمكافحة الفساد</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:29:57.283081+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/news-details/15/2</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>خبر للتغطية الاعلامية
+																		رجوع									
+									١٣ كانون الأول ، ٢٠١٦ 
+									إتصل اللواء أشرف ريفي بمدعي التمييز القاضي سمير حمود، وتابع معه سير التحقيق في الانفجار الذي استهدف بنك لبنان والمهجر، كما إتصل برئيس مجلس إدارة المصرف سعد الأزهري، مستنكراً هذا الاستهداف، الذي يطال القطاع المصرفي، ومؤكداً الدعم الكامل لمصرف لبنان والمصارف اللبنانية في وجه ما تتعرض له من ضغوط وتهديدات</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:30:03.901566+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/news-details/16/2</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>ريفي اتصل بحمود وتابع مجريات التحقيق
+																		رجوع									
+									١٢ كانون الأول ، ٢٠١٦ 
+									إتصل اللواء أشرف ريفي بالمدعي العام التمييزي القاضي سمير حمود واطلع منه على مجريات التحقيق في الجريمة المروعة التي وقع ضحيتها الشاب حسين الحجيري، وأكد ريفي على حتمية أن تأخذ العدالة مجراها، وأن يحاسَب المسؤول عن إرتكاب الجريمة
+واعتبر ريفي ان المغدور حسين الحجيري هو شهيد كل لبنان، حيث سقط ظلماً ضحية للثأر، وشهادته تضاف الى شهادة عناصر الجيش الذين استشهدوا غدراً على يد الارهاب، وجريمة قتله هي عمل انتقامي مجرم وخارج عن كل القيم والاعراف الانسانية
+أضاف: لقد طالت هذه الجريمة مواطناً بريئاً لا ذنب له، فضلاً عن انها شكلت نموذجاً بائداً يبيح شريعة الغاب، وانتهاكاً صارخاً للعدالة، وسلوكاً مرفوضاً دينياً واخلاقياً وقانونياً، خصوصاً بعدما تلاها من مظاهر وعراضات، ضاعفت من هول الجريمة وفظاعتها وختم بالتوجه الى اهل عرسال بالقول: نقدم التعازي لاهلنا في عرسال الأبية الذين نتشارك معهم المعاناة التي يعيشونها، ونؤكد لهم الاصرار على تحقيق العدالة، ومحاسبة من ارتكب هذه الجريمة</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:30:10.516080+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/news-details/19/2</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>ريفي إلتقى أبوالغيط ومسؤولين مصريين
+																		رجوع									
+									١٠ كانون الأول ، ٢٠١٦ 
+									واصل اللواء أشرف ريفي زيارته إلى القاهرة والتقى أمين عام "جامعة الدول العربية" أحمد أبو الغيط وعرض معه الأوضاع في لبنان والمنطقة العربية ، ثم إلتقى وزير العدل المصري محمد حسام عبد الرحيم بحضور السفير عبد الرحمن الصلح رئيس "المركز العربي للدراسات القانونية والقضائية" .
+بعد ذلك إلتقى رئيس مجلس الدولة المستشار الدكتور جمال ندا .</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:30:17.121103+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/news-details/12/2</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>ترأس اللواء أشرف ريفي وفداً قضائياً مؤلفاً من رئيس مجلس القضاء الأعلى القاضي جان فهد والنائب العام التمييزي القاضي سمير حمود ورئيس هيئة التفتيش القضائي القاضي أكرم بعاصيري والمديرة العامة لوزراة العدل القاضي ميسم النويري ورئيسة معهد الدروس القضائية القاضي ندى دكروب والقاضي محمد مرتضى ومستشارَي اللواء القاضي محمد صعب والمحامي هاني المرعبي ومدير مكتبه الرائد محمد الرفاعي للمشاركة في مؤتمر القانون الدولي الذي يُعقد في إسطنبول من 17 الى 19 تشرين الأول بحضور وزراء عدل عرب وأجانب وممثلين عن 34 دولة
+إفتتحت أعمال المؤتمر بحفل جمع كافة الوفود المشاركة برعاية وحضور الرئيس التركي رجب طيب أردوغان حيث ألقى كلمة تطرق فيها الى الوضع التركي والإقليمي والدولي ولا سيما الأحداث المستجدة في سوريا والعراق
+وقد شارك أعضاء الوفد في كافة الندوات والمحاضرات وكانت لهم مداخلات في مواضيع مختلفة من وساطة وتحكيم والهيكلة القضائية وهيكلة النيابات العامة وسبل تدريب القضاة وتطويرها وتسريع المحاكمات
+وترأس اللواء ريفي اليوم جلسة حول موضوع حقوق الضحايا في قضايا الارهاب كان فيها مداخلات لخبراء أميريكيين وبريطانيين وأتراك
+وعلى هامش المؤتمر التقى اللواء ريفي وزير العدل التركي باكير موزداغ حيث عُقدت جلسة إستثنائية مطولة بحث فيها الطرفان في ضرورة تنظيم تعاون قضائي بين البلدين
+وقدم الوزير التركي درعاً تقديرياً للواء ريفي تكريماً له وشكر الأخير بدوره وزارة العدل التركية لتنظيم هذا المؤتمر على أمل أن يبقى التنسيق مستمراً بينهما</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:30:24.232657+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/news-details/13/2</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>ريفي يعقد مؤتمر لتعزيز النزاهة ومكافحة الفساد
+																		رجوع									
+									٠٥ أيلول ، ٢٠١٦ 
+									ريفي يعقد إجتماعاً تحضيرياً للمؤتمر الخامس ل"الشبكة العربية لتعزيز النزاهة ومكافحة الفساد "
+بصفته رئيساً للشبكة العربية لتعزيز النزاهة ومكافحة الفساد ، عقد اللواء أشرف ريفي إجتماعاً ضمَّ الوزارات والهيئات النقابية اللبنانية المنضمة إلى الشبكة ، وذلك تحضيراً لمؤتمرها الخامس الذي تستضيفه تونس من 5 إلى 7 أيلول تحت رعاية رئيس الحكومة التونسية ، وبالتعاون مع الأمم المتحدة ، وبحضور وزراء ومسؤولين وناشطين من أكثر من ثلاثين دولة ومنظمة إقليمية ودولية . 
+شارك في الإجتماع التحضيري رئيس التفتيش المركزي القاضي جورج عواد ، ورئيس الهيئة العليا للتأديب القاضي مروان عبود ، والمديرة العامة في وزارة العدل القاضية ميسم النويري ، والقاضي بسام وهبة ممثلاً عن ديوان المحاسبة ، والمحامي شربل سركيس ممثلاً عن مكتب وزير الدولة لشؤون التنمية الإدارية ، والقاضية رنا عاكوم ضابط إتصال وزير العدل في الشبكة ، بالإضافة إلى الأستاذ أركان السبلاني والسيدة ناتاشا سركيس من المكتب الإقليمي لبرنامج الأمم المتحدة .
+إستعرض المشاركون برنامج المؤتمر الوزاري الذي ينعقد تحت عنوان " تفعيل المساءلة للنهوض بالتنمية في البلدان العربية " ، وتباحثوا في أبرز المستجدات والتحديات ذات الصلة في لبنان ، وفي كيفية إعداد الوفد اللبناني للمساهمة في فعاليات المؤتمر للإستفادة منه ، لا سيما وأنه سيرسم خطة تعاون على الصعيد الإقليمي في هذا المجال للسنتين القادمتين ، وسيشهد أيضاً إنتقال رئاسة الشبكة إلى الجمهورية التونسية
+يُذكر أن الشبكة العربية تُعَدّ الآلية العربية الأبرز التي تُعنى بتعزيز النزاهة ومكافحة الفساد ، وتعمل على دعم الدول العربية لتنفيذ الإتفاقيات الأممية والإقليمية ذات الصلة وبناء القدرات الوطنية في هذا المجال . تضم الشبكة 47 وزارة وهيئة من 18 بلداً عربياً وعضوين مراقبين هما البرازيل وماليزيا ومحموعة غير حكومية مؤلفة من 23 منظمة مستقلة من المجتمع المدني والقطاع الخاص والمجال الأكاديمي</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:30:30.717067+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>justicegov- أخبار ونشاطات</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://www.justice.gov.lb/index.php/news-details/17/2</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>ترأس وزير العدل اللواء أشرف ريفي رئيس مجلس إدارة المركز العربي للبحوث القانونية والقضائية إجتماع المركز المنعقد في القاهرة بتاريخ 18 نيسان 2016 بحضور السفير عبد الرحمن الصلح الأمين العام المساعد ، رئيس ومقرر  المركز ، السفير وجيه حنفي ، الأمين العام المساعد ورئيس قطاع الشؤون القانونية ورئيس الأمانة الفنية للمجلس الدكتور أحمد الشافعي مستشار المحكمة العليا ومدير مركز البحوث القانونية  القضائية في الجزائر والأستاذ محمد صالح البكري مستشار وزير العدل في جيبوتي.
+ويتركز عمل المركز على تحقيق أهداف مجلس وزراء العدل العرب .وعلى تخطي مرحلة الصعوبة بعد وضعه بعهدة هذا المجلس رغم النقص الفادح في موارده البشرية والمادية  
+بدايةً  وجه الأمين العام السفير وجيه حنفي الشكر والتقدير لرئيس مجلس إدارة المركز اللواء أشرف ريفي لحرصه على .الحضور  
+وتمنى حنفي دعم وتطوير المركز بالإمكانيات والوسائل التي تمكنه من أداء وظيفته بشكلٍ كامل .
+بعدها إنتقل المشاركون لمناقشة جدول الأعمال والأنشطة المقررة كما تم عرض مشاريع التوصيات وإقرار اللازم منها وفي الختام توجه أعضاء مجلس إدارة المركز بالشكر والتقدير للواء أشرف ريفي رئيس مجلس الإدارة على الجهود التي بذلها</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:30:38.359183+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
